--- a/city_finance_analysis/city_finance_analysis/output/宽表_分城市相关性.xlsx
+++ b/city_finance_analysis/city_finance_analysis/output/宽表_分城市相关性.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,38 +429,38 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sales_corr</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>invest_corr</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>price_corr</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>area_corr</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.2012602736035299</v>
+        <v>-0.20126027360353</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2080452600436363</v>
+        <v>-0.2080452600436362</v>
       </c>
       <c r="D2" t="n">
         <v>0.499167648116067</v>
@@ -458,45 +470,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>乌鲁木齐</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05137637842363003</v>
+        <v>0.05137637842363005</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4950081351489378</v>
+        <v>0.495008135148938</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7622833318572271</v>
+        <v>0.762283331857227</v>
       </c>
       <c r="E3" t="n">
-        <v>0.384991945793671</v>
+        <v>0.3849919457936709</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>兰州</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4972923298211629</v>
+        <v>0.497292329821163</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5596752493418764</v>
+        <v>0.5596752493418765</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7363805626431033</v>
+        <v>0.7363805626431034</v>
       </c>
       <c r="E4" t="n">
         <v>0.5892385658054564</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
@@ -515,7 +527,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>南京</t>
         </is>
@@ -527,33 +539,33 @@
         <v>0.359058565223116</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5731148382179586</v>
+        <v>0.5731148382179585</v>
       </c>
       <c r="E6" t="n">
         <v>-0.3770874463494323</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>南宁</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.461257954461801</v>
+        <v>0.4612579544618009</v>
       </c>
       <c r="C7" t="n">
         <v>0.4602594310354446</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7499031130866629</v>
+        <v>0.749903113086663</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6510823704286705</v>
+        <v>0.6510823704286708</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>南昌</t>
         </is>
@@ -562,17 +574,17 @@
         <v>0.592770676105526</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3261859855213789</v>
+        <v>0.3261859855213788</v>
       </c>
       <c r="D8" t="n">
         <v>0.9271276662804101</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7133079923461434</v>
+        <v>0.7133079923461435</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>厦门</t>
         </is>
@@ -591,35 +603,35 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>合肥</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.3417685465817554</v>
+        <v>-0.3417685465817553</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.8094790461087671</v>
+        <v>-0.8094790461087668</v>
       </c>
       <c r="D10" t="n">
-        <v>0.591801286229494</v>
+        <v>0.5918012862294938</v>
       </c>
       <c r="E10" t="n">
         <v>0.383031598894404</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>呼和浩特</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2866603549179367</v>
+        <v>0.2866603549179366</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.6989291872910777</v>
+        <v>-0.6989291872910774</v>
       </c>
       <c r="D11" t="n">
         <v>0.8215074632876682</v>
@@ -629,13 +641,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>哈尔滨</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02311297248630116</v>
+        <v>0.02311297248630113</v>
       </c>
       <c r="C12" t="n">
         <v>-0.2404899582776842</v>
@@ -648,7 +660,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>大连</t>
         </is>
@@ -657,7 +669,7 @@
         <v>-0.3910424236470989</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.573124517474257</v>
+        <v>-0.5731245174742571</v>
       </c>
       <c r="D13" t="n">
         <v>0.6623600226103173</v>
@@ -667,7 +679,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>天津</t>
         </is>
@@ -679,90 +691,90 @@
         <v>0.4892658595724457</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8595323272136952</v>
+        <v>0.8595323272136949</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0908197157311373</v>
+        <v>0.09081971573113728</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>太原</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4711834564274496</v>
+        <v>0.4711834564274495</v>
       </c>
       <c r="C15" t="n">
         <v>0.1893330062135594</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6686777245338579</v>
+        <v>0.6686777245338578</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5901684216032941</v>
+        <v>0.590168421603294</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>宁波</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02489555997018846</v>
+        <v>0.02489555997018851</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5131891849887199</v>
+        <v>0.51318918498872</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5598994636158082</v>
+        <v>0.5598994636158081</v>
       </c>
       <c r="E16" t="n">
         <v>0.2666802867849322</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2415754136242359</v>
+        <v>0.2415754136242358</v>
       </c>
       <c r="C17" t="n">
         <v>0.9263359643935147</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8208725646046483</v>
+        <v>0.8208725646046485</v>
       </c>
       <c r="E17" t="n">
-        <v>0.08262657389681601</v>
+        <v>0.08262657389681596</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2943670831229508</v>
+        <v>0.2943670831229509</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.034666862191951</v>
+        <v>-0.03466686219195101</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.08306893986808542</v>
+        <v>-0.08306893986808543</v>
       </c>
       <c r="E18" t="n">
         <v>0.1628758108550413</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>拉萨</t>
         </is>
@@ -773,7 +785,7 @@
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>昆明</t>
         </is>
@@ -782,17 +794,17 @@
         <v>-0.2862370830173355</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.02215145374267343</v>
+        <v>-0.02215145374267339</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.04135373845898211</v>
+        <v>-0.04135373845898212</v>
       </c>
       <c r="E20" t="n">
         <v>-0.1375500415276017</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
@@ -804,14 +816,14 @@
         <v>0.4483387331387423</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7986585134337336</v>
+        <v>0.7986585134337334</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4682179800082069</v>
+        <v>0.4682179800082067</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
@@ -823,20 +835,20 @@
         <v>-0.339983163664165</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4578818011149446</v>
+        <v>0.4578818011149448</v>
       </c>
       <c r="E22" t="n">
         <v>0.04094104271111658</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>沈阳</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07865364263195358</v>
+        <v>-0.0786536426319536</v>
       </c>
       <c r="C23" t="n">
         <v>-0.6235749520233193</v>
@@ -849,7 +861,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>济南</t>
         </is>
@@ -861,14 +873,14 @@
         <v>0.4490749033202852</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7282521886817962</v>
+        <v>0.7282521886817963</v>
       </c>
       <c r="E24" t="n">
-        <v>0.544935032255832</v>
+        <v>0.5449350322558318</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>海口</t>
         </is>
@@ -887,108 +899,108 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4989281065623838</v>
+        <v>0.4989281065623837</v>
       </c>
       <c r="C26" t="n">
         <v>0.2293430900361481</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4572370509492039</v>
+        <v>0.4572370509492038</v>
       </c>
       <c r="E26" t="n">
         <v>0.2444494232112326</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>石家庄</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7744330735666564</v>
+        <v>0.7744330735666566</v>
       </c>
       <c r="C27" t="n">
         <v>0.2329392402259454</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9086729247399944</v>
+        <v>0.9086729247399943</v>
       </c>
       <c r="E27" t="n">
         <v>0.439351649628164</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>福州</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3108311884160497</v>
+        <v>0.3108311884160498</v>
       </c>
       <c r="C28" t="n">
-        <v>0.224237886886857</v>
+        <v>0.2242378868868571</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6870018017917788</v>
+        <v>0.6870018017917791</v>
       </c>
       <c r="E28" t="n">
         <v>0.6180973534266231</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>西宁</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4346294430804976</v>
+        <v>0.4346294430804974</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5408210922539165</v>
+        <v>0.5408210922539164</v>
       </c>
       <c r="D29" t="n">
         <v>0.4682332350833699</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6426936034399848</v>
+        <v>0.6426936034399847</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>西安</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.45866938385747</v>
+        <v>0.4586693838574699</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3714797098267206</v>
+        <v>-0.3714797098267207</v>
       </c>
       <c r="D30" t="n">
-        <v>0.804232680483827</v>
+        <v>0.8042326804838271</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5056123973765377</v>
+        <v>0.5056123973765378</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>贵阳</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4032554882742757</v>
+        <v>0.4032554882742758</v>
       </c>
       <c r="C31" t="n">
         <v>0.1462008192580852</v>
@@ -997,11 +1009,11 @@
         <v>0.2739671769166392</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1682606138190223</v>
+        <v>0.1682606138190224</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>郑州</t>
         </is>
@@ -1010,17 +1022,17 @@
         <v>0.8587430593324594</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8285618105097274</v>
+        <v>0.8285618105097277</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7764788694240405</v>
+        <v>0.7764788694240407</v>
       </c>
       <c r="E32" t="n">
         <v>0.9567313057084686</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>重庆</t>
         </is>
@@ -1029,55 +1041,55 @@
         <v>0.3067773146837716</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4445316053448286</v>
+        <v>0.4445316053448287</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5625381416556109</v>
+        <v>0.5625381416556111</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5938043227328506</v>
+        <v>0.5938043227328504</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>银川</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.09415425761665963</v>
+        <v>-0.09415425761665967</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.006151844692739467</v>
+        <v>-0.00615184469273945</v>
       </c>
       <c r="D34" t="n">
         <v>0.4840804446070193</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5269124517046279</v>
+        <v>0.5269124517046277</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>长春</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.2941599450057212</v>
+        <v>0.2941599450057211</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2393089684027164</v>
+        <v>-0.2393089684027165</v>
       </c>
       <c r="D35" t="n">
-        <v>0.753418171371376</v>
+        <v>0.7534181713713761</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2611814438200843</v>
+        <v>0.2611814438200845</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>长沙</t>
         </is>
@@ -1096,7 +1108,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>青岛</t>
         </is>
@@ -1111,7 +1123,7 @@
         <v>0.8218141358912577</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7539198952775299</v>
+        <v>0.75391989527753</v>
       </c>
     </row>
   </sheetData>
